--- a/excel_import_sample_all_types.xlsx
+++ b/excel_import_sample_all_types.xlsx
@@ -424,20 +424,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="56" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,35 +464,40 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>分值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>题干</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>选项A</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>选项B</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>选项C</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>选项D</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>正确答案</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
@@ -516,37 +522,40 @@
       <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>求 f(x)=x^2 的导数。</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>2x</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>x^2</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>幂函数求导，x^2 的导数为 2x。</t>
         </is>
@@ -571,37 +580,40 @@
       <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>以下哪些属于 Python 的循环语句？</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>for</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>while</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>if</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>switch</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>A,B</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>for 和 while 都是循环；if 是条件判断，switch 不是 Python 关键字。</t>
         </is>
@@ -626,21 +638,22 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>地球围绕太阳公转。</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>判断题会自动生成 A=正确、B=错误；本题答案应为 A。</t>
         </is>
@@ -665,21 +678,22 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>请填写成语：锲而不____。</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>舍</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>填空题无需填写选项 A-D，正确答案直接写文本即可。</t>
         </is>
@@ -704,21 +718,24 @@
       <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>请填写短语：look forward to ____ from you.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>hearing</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>填空题支持直接填写文本答案。</t>
         </is>
@@ -752,6 +769,13 @@
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
+        <is>
+          <t>分值列可留空，留空时导入后使用配置文件中的题型默认分值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Excel 导入适合纯文本题目；公式、图片、代码题建议在网页端编辑。</t>
         </is>
